--- a/414-rc---contact/ig/ValueSet-tddui-contact-relation.xlsx
+++ b/414-rc---contact/ig/ValueSet-tddui-contact-relation.xlsx
@@ -44,7 +44,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>TDDUI Relation</t>
+    <t>TDDUI Contact Relation</t>
   </si>
   <si>
     <t>Status</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T16:24:47+00:00</t>
+    <t>2026-02-02T09:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/ValueSet-tddui-contact-relation.xlsx
+++ b/414-rc---contact/ig/ValueSet-tddui-contact-relation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:56:46+00:00</t>
+    <t>2026-02-04T09:47:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/ValueSet-tddui-contact-relation.xlsx
+++ b/414-rc---contact/ig/ValueSet-tddui-contact-relation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T09:47:16+00:00</t>
+    <t>2026-02-04T14:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/ValueSet-tddui-contact-relation.xlsx
+++ b/414-rc---contact/ig/ValueSet-tddui-contact-relation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:08:59+00:00</t>
+    <t>2026-02-04T16:27:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
